--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>57567.36</v>
+        <v>56458.54</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24751.65</v>
+        <v>24274.9</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45946.04</v>
+        <v>44886.68</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29849.98</v>
+        <v>29161.74</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12632.89</v>
+        <v>12457.32</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36497.24</v>
+        <v>36053.38</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>24640.53</v>
+        <v>24340.87</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>55666.44</v>
+        <v>54989.46</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>49488.86</v>
+        <v>48887.01</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>295182.2</v>
+        <v>291592.37</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>74735.08</v>
+        <v>73826.19</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>27670.74</v>
+        <v>27289.32</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35146.84</v>
+        <v>34662.36</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16722.68</v>
+        <v>16696.03</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>22993.68</v>
+        <v>22957.04</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>59467.99</v>
+        <v>59373.22</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38393.22</v>
+        <v>38456.04</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>36371.82</v>
+        <v>36431.33</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>20903.34</v>
+        <v>20937.55</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17783.4</v>
+        <v>17774.5</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7913.17</v>
+        <v>7909.21</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20416.71</v>
+        <v>20406.49</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21689.45</v>
+        <v>21678.6</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>49521.64</v>
+        <v>49351.13</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>52482.23</v>
+        <v>52201.04</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>15156.18</v>
+        <v>15074.98</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>580026</v>
+        <v>576310.49</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8407.74</v>
+        <v>8353.889999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8361.34</v>
+        <v>8414.41</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>25585.69</v>
+        <v>25748.1</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>54069.98</v>
+        <v>54413.21</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1798.14</v>
+        <v>1821.86</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>66626.96000000001</v>
+        <v>67506.00999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16049.59</v>
+        <v>16286.38</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>654773.7</v>
+        <v>664434.1899999999</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15374.07</v>
+        <v>15739.62</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>51350.45</v>
+        <v>52571.41</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11315.89</v>
+        <v>11584.95</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>25623.45</v>
+        <v>26232.71</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>36524</v>
+        <v>37425.15</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22959.37</v>
+        <v>23640.04</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>31260.61</v>
+        <v>32166.56</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>30108.34</v>
+        <v>30980.89</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>21844.69</v>
+        <v>22477.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>Adolfo Ignacio</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>Ximena</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -623,7 +623,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>96.986.170-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>76.572.009-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>76.572.009-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2127,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2314,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2440,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2570,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2635,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2700,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2887,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3013,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ene-2026.xlsx
@@ -1066,7 +1066,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1127,7 +1131,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
